--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -799,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -826,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -853,7 +868,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,83 +907,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1615800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>196129.76</t>
+          <t>1765800</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>136650</t>
+          <t>214093.83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>136650</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>59479.76</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>77443.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,83 +934,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1765800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>214093.83</t>
+          <t>1765800</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>136650</t>
+          <t>214093.83</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>154614</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>77443.83</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>59479.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +856,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +883,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -895,7 +910,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -907,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -922,7 +937,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -934,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,83 +976,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1765800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>214093.83</t>
+          <t>2085800</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>154614</t>
+          <t>252417.18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>154614</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>59479.83</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>97803.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -706,12 +706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1003,83 +1003,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2085800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>252417.18</t>
+          <t>2085800</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>154614</t>
+          <t>252417.18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>192937</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>97803.18</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>59480.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -814,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -841,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -868,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -895,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +925,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -922,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -937,7 +952,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -949,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -964,7 +979,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -976,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -991,7 +1006,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1003,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1030,83 +1045,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2085800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>252417.18</t>
+          <t>2135800</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>192937</t>
+          <t>258299.54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>192937</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>59480.18</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>65362.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,83 +1072,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2135800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>258299.54</t>
+          <t>2135800</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>192937</t>
+          <t>258299.54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>193625</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>65362.54</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>64674.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -748,12 +748,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +937,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1045,12 +1045,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1072,12 +1072,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1099,83 +1099,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2135800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>258299.54</t>
+          <t>2135800</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>193625</t>
+          <t>258299.54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>198819</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>64674.54</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>59480.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -790,7 +805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +832,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -856,12 +871,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -883,12 +898,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -910,12 +925,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -937,12 +952,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,12 +979,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -991,12 +1006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1006,7 +1021,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1018,12 +1033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1033,7 +1048,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1045,12 +1060,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1060,7 +1075,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1072,12 +1087,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1087,7 +1102,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1099,12 +1114,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1126,83 +1141,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2135800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>258299.54</t>
+          <t>2745800</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>329229.77</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>198819</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>59480.54</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>130410.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -832,7 +847,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -859,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -898,12 +913,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -925,12 +940,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -952,12 +967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -979,12 +994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1006,12 +1021,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1033,12 +1048,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1048,7 +1063,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1060,12 +1075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1075,7 +1090,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1087,12 +1102,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1102,7 +1117,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1114,12 +1129,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1129,7 +1144,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1141,12 +1156,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1168,83 +1183,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2745800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>329229.77</t>
+          <t>3355800</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>402723.74</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>198819</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>130410.77</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>203904.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -874,7 +889,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -940,12 +955,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -967,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -994,12 +1009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1021,12 +1036,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1048,12 +1063,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1075,12 +1090,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1090,7 +1105,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1102,12 +1117,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1117,7 +1132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1129,12 +1144,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1144,7 +1159,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1156,12 +1171,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1171,7 +1186,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1183,12 +1198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1210,83 +1225,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3355800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>402723.74</t>
+          <t>3355801</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>402724.74</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>198819</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>203904.74</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>203905.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,193 +747,223 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/24 08:03:39</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>12269.94</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/24 08:03:39</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>5194</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -955,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1009,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1036,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1063,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1090,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1117,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1132,7 +1162,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1144,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1186,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1198,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1225,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1240,7 +1270,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1252,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/24 09:45:46</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>46380</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1276,59 +1306,113 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3355801</t>
-        </is>
-      </c>
-    </row>
+          <t>08/24 09:45:46</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>402724.74</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>3965801</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>476664.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>198819</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>203905.74</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>277845.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -958,12 +958,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -985,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1012,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1282,12 +1282,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1336,83 +1336,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3965801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>476664.14</t>
+          <t>3965801</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>476664.14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>272758</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>277845.14</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>203906.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1042,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1054,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1066,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1093,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1120,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1174,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1201,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1228,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1243,7 +1258,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1255,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1270,7 +1285,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1282,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1297,7 +1312,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1309,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1324,7 +1339,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1336,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1363,83 +1378,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3965801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>476664.14</t>
+          <t>4115801</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>272758</t>
+          <t>494311.2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>272758</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>203906.14</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>221553.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1000,12 +1000,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1405,83 +1405,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>4115801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>494311.2</t>
+          <t>4115801</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>272758</t>
+          <t>494311.2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>290405</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>221553.2</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>203906.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 22:52:29</t>
+          <t>10/17 11:22:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1108,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1123,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1135,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1162,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1189,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1216,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1243,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1270,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1297,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1312,7 +1327,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1324,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1351,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1366,7 +1381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1378,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1393,7 +1408,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1405,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1432,83 +1447,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4115801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>494311.2</t>
+          <t>4215801</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>290405</t>
+          <t>506075.9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>290405</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>203906.2</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>215670.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1042,12 +1042,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1285,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1420,12 +1420,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1474,83 +1474,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>4215801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>506075.9</t>
+          <t>4215801</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>290405</t>
+          <t>506075.9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>302169</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>215670.9</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>203906.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/17 11:22:50</t>
+          <t>10/20 16:11:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 22:52:29</t>
+          <t>10/17 11:22:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1123,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1150,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1165,7 +1180,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1177,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1192,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1204,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1231,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1258,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1285,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1312,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1339,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1366,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1381,7 +1396,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1393,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1408,7 +1423,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1420,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1435,7 +1450,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1447,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1462,7 +1477,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1501,83 +1516,110 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4215801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>506075.9</t>
+          <t>4315801</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>302169</t>
+          <t>518124.1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>302169</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>203906.9</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>215955.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,83 +1543,110 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>4315801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>518124.1</t>
+          <t>4315801</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>302169</t>
+          <t>518124.1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>314217</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>215955.1</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>203907.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 16:11:58</t>
+          <t>10/23 10:37:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/17 11:22:50</t>
+          <t>10/20 16:11:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/30 22:52:29</t>
+          <t>10/17 11:22:50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1249,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1276,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1465,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1477,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1489,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1531,7 +1546,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,83 +1585,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>4315801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>518124.1</t>
+          <t>4365801</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>314217</t>
+          <t>524076.48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>314217</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>203907.1</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>209859.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1126,12 +1126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,83 +1612,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4365801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>524076.48</t>
+          <t>4365801</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>314217</t>
+          <t>524076.48</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>314445</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>209859.48</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>209631.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1126,12 +1126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,83 +1639,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>4365801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>524076.48</t>
+          <t>4365801</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>314445</t>
+          <t>524076.48</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>320169</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>209631.48</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>203907.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/23 10:37:09</t>
+          <t>10/27 10:13:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/20 16:11:58</t>
+          <t>10/23 10:37:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/17 11:22:50</t>
+          <t>10/20 16:11:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/30 22:52:29</t>
+          <t>10/17 11:22:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/23 13:39:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1315,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1345,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1357,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1369,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1450,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1531,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1546,7 +1561,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1600,7 +1615,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1627,7 +1642,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,83 +1681,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>4365801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>524076.48</t>
+          <t>4415801</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>320169</t>
+          <t>530028.86</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>320169</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>203907.48</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>209859.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1168,12 +1168,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/23 13:39:54</t>
+          <t>10/27 10:13:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1708,83 +1708,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>4415801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>530028.86</t>
+          <t>4415801</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>320169</t>
+          <t>530028.86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>320407</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>209859.86</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>209621.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1168,12 +1168,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/27 10:13:41</t>
+          <t>10/27 11:57:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/23 13:39:54</t>
+          <t>10/27 10:13:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1438,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,83 +1735,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>4415801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>530028.86</t>
+          <t>4415801</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>320407</t>
+          <t>530028.86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>326121</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>209621.86</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>203907.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 10:13:36</t>
+          <t>10/30 09:54:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>14457.83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/23 10:37:09</t>
+          <t>10/27 10:13:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/20 16:11:58</t>
+          <t>10/23 10:37:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/17 11:22:50</t>
+          <t>10/20 16:11:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/30 22:52:29</t>
+          <t>10/17 11:22:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 20:04:01</t>
+          <t>09/24 20:04:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72727.27</t>
+          <t>1212.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24 20:02:59</t>
+          <t>09/24 20:04:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72727.27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>kefu111kf</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 19:09:58</t>
+          <t>09/24 20:02:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>kefu111kf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/27 11:57:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/27 10:13:41</t>
+          <t>10/27 11:57:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/23 13:39:54</t>
+          <t>10/27 10:13:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1291,7 +1306,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1303,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1384,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1411,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1438,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1453,7 +1468,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1465,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1492,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1519,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1573,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1642,7 +1657,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1669,7 +1684,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1696,7 +1711,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1723,7 +1738,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1762,83 +1777,110 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>4415801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>530028.86</t>
+          <t>4535801</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>326121</t>
+          <t>544486.69</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>326121</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>203907.86</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>218365.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -1210,12 +1210,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/27 11:57:45</t>
+          <t>10/30 12:44:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/27 10:13:41</t>
+          <t>10/27 11:57:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/23 13:39:54</t>
+          <t>10/27 10:13:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
+          <t>10/23 13:39:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/20 17:14:32</t>
+          <t>10/23 10:38:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/17 12:34:59</t>
+          <t>10/20 17:14:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>10/17 12:34:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1426,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21 15:43:17</t>
+          <t>09/24 21:10:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
+          <t>09/21 15:43:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/18 21:26:48</t>
+          <t>09/21 14:33:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>688</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17 16:37:05</t>
+          <t>09/18 21:26:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/11 12:03:55</t>
+          <t>09/17 16:37:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1804,83 +1804,110 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>4535801</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>544486.69</t>
+          <t>4535801</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>326121</t>
+          <t>544486.69</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>340578</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>218365.69</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>203908.69</t>
         </is>
       </c>
     </row>
